--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43E9378-884D-4F8F-B67A-90BEECD14921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2DCC19-0668-4A74-B516-C86A323E9B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4778" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="81">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -852,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3041,6 +3041,29 @@
         <v>59</v>
       </c>
     </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2026</v>
+      </c>
+      <c r="B101" t="s">
+        <v>75</v>
+      </c>
+      <c r="C101">
+        <v>1117</v>
+      </c>
+      <c r="D101">
+        <v>684</v>
+      </c>
+      <c r="E101">
+        <v>143</v>
+      </c>
+      <c r="F101">
+        <v>103</v>
+      </c>
+      <c r="G101" s="17">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3049,7 +3072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5273,6 +5296,52 @@
       </c>
       <c r="G100">
         <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>2026</v>
+      </c>
+      <c r="B101" t="s">
+        <v>73</v>
+      </c>
+      <c r="C101">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D101">
+        <v>4.92</v>
+      </c>
+      <c r="E101">
+        <v>4.76</v>
+      </c>
+      <c r="F101">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G101">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2026</v>
+      </c>
+      <c r="B102" t="s">
+        <v>75</v>
+      </c>
+      <c r="C102">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D102">
+        <v>4.91</v>
+      </c>
+      <c r="E102">
+        <v>4.78</v>
+      </c>
+      <c r="F102">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G102">
+        <v>4.9000000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -5283,7 +5352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2281"/>
+  <dimension ref="A1:L2331"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -50954,6 +51023,1006 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2282" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2282" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2282" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2282" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2282" s="3">
+        <v>919</v>
+      </c>
+      <c r="F2282" s="9">
+        <v>0.91500000000000004</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2283" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2283" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2283" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2283" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2283" s="3">
+        <v>75</v>
+      </c>
+      <c r="F2283" s="9">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2284" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2284" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2284" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2284" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2284" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2284" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2285" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2285" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2285" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2285" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2285" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2285" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2286" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2286" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2286" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2286" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2286" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2286" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2287" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2287" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2287" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2287" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2287" s="3">
+        <v>792</v>
+      </c>
+      <c r="F2287" s="9">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2288" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2288" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2288" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2288" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2288" s="3">
+        <v>57</v>
+      </c>
+      <c r="F2288" s="9">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2289" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2289" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2289" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2289" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2289" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2289" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2290" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2290" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2290" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2290" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2290" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2290" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2291" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2291" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2291" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2291" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2291" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2291" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2292" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2292" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2292" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2292" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2292" s="3">
+        <v>84</v>
+      </c>
+      <c r="F2292" s="9">
+        <v>0.80800000000000005</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2293" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2293" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2293" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2293" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2293" s="3">
+        <v>16</v>
+      </c>
+      <c r="F2293" s="9">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2294" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2294" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2294" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2294" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2294" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2294" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2295" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2295" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2295" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2295" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2295" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2295" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2296" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2296" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2296" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2296" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2296" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2296" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2297" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2297" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2297" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2297" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2297" s="3">
+        <v>123</v>
+      </c>
+      <c r="F2297" s="9">
+        <v>0.91800000000000004</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2298" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2298" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2298" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2298" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2298" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2298" s="9">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2299" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2299" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2299" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2299" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2299" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2299" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2300" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2300" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2300" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2300" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2300" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2300" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2301" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2301" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2301" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2301" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2301" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2301" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2302" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2302" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2302" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2302" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2302" s="3">
+        <v>58</v>
+      </c>
+      <c r="F2302" s="9">
+        <v>0.98299999999999998</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2303" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2303" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2303" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2303" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2303" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2303" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2304" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2304" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2304" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2304" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2304" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2304" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2305" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2305" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2305" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2305" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2305" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2305" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2306" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2306" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2306" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2306" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2306" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2306" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2307" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2307" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2307" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2307" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2307" s="3">
+        <v>1029</v>
+      </c>
+      <c r="F2307" s="9">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2308" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2308" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2308" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2308" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2308" s="3">
+        <v>73</v>
+      </c>
+      <c r="F2308" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2309" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2309" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2309" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2309" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2309" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2309" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2310" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2310" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2310" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2310" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2310" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2310" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2311" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2311" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2311" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2311" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2311" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2311" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2312" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2312" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2312" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2312" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2312" s="3">
+        <v>634</v>
+      </c>
+      <c r="F2312" s="9">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2313" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2313" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2313" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2313" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2313" s="3">
+        <v>42</v>
+      </c>
+      <c r="F2313" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2314" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2314" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2314" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2314" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2314" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2314" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2315" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2315" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2315" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2315" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2315" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2315" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2316" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2316" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2316" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2316" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2316" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2316" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2317" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2317" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2317" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2317" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2317" s="3">
+        <v>117</v>
+      </c>
+      <c r="F2317" s="9">
+        <v>0.81799999999999995</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2318" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2318" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2318" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2318" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2318" s="3">
+        <v>23</v>
+      </c>
+      <c r="F2318" s="9">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2319" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2319" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2319" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2319" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2319" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2319" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2320" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2320" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2320" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2320" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2320" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2320" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2321" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2321" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2321" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2321" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2321" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2321" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2322" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2322" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2322" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2322" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2322" s="3">
+        <v>95</v>
+      </c>
+      <c r="F2322" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2323" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2323" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2323" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2323" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2323" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2323" s="9">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2324" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2324" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2324" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2324" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2324" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2324" s="9">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2325" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2325" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2325" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2325" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2325" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2325" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2326" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2326" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2326" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2326" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2326" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2326" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2327" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2327" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2327" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2327" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2327" s="3">
+        <v>88</v>
+      </c>
+      <c r="F2327" s="9">
+        <v>0.90700000000000003</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2328" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2328" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2328" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2328" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2328" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2328" s="9">
+        <v>8.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2329" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2329" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2329" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2329" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2329" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2329" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2330" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2330" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2330" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2330" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2330" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2330" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2331" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2331" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2331" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2331" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2331" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2331" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2DCC19-0668-4A74-B516-C86A323E9B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE44447-9408-4C4B-B6AF-5D8A8C4EC206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4932" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -308,6 +308,10 @@
   </si>
   <si>
     <t>14w</t>
+  </si>
+  <si>
+    <t>10w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -852,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3062,6 +3066,29 @@
       </c>
       <c r="G101" s="17">
         <v>97</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2026</v>
+      </c>
+      <c r="B102" t="s">
+        <v>76</v>
+      </c>
+      <c r="C102">
+        <v>1361</v>
+      </c>
+      <c r="D102">
+        <v>755</v>
+      </c>
+      <c r="E102">
+        <v>102</v>
+      </c>
+      <c r="F102">
+        <v>165</v>
+      </c>
+      <c r="G102" s="17">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -5326,22 +5353,22 @@
         <v>2026</v>
       </c>
       <c r="B102" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C102">
-        <v>4.9000000000000004</v>
+        <v>4.91</v>
       </c>
       <c r="D102">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="E102">
-        <v>4.78</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="F102">
         <v>4.9000000000000004</v>
       </c>
       <c r="G102">
-        <v>4.9000000000000004</v>
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -5352,7 +5379,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2331"/>
+  <dimension ref="A1:L2356"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -52023,6 +52050,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2332" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2332" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2332" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2332" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2332" s="3">
+        <v>1254</v>
+      </c>
+      <c r="F2332" s="9">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2333" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2333" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2333" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2333" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2333" s="3">
+        <v>92</v>
+      </c>
+      <c r="F2333" s="9">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2334" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2334" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2334" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2334" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2334" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2334" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2335" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2335" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2335" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2335" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2335" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2335" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2336" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2336" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2336" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2336" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2336" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2336" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2337" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2337" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2337" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2337" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2337" s="3">
+        <v>706</v>
+      </c>
+      <c r="F2337" s="9">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2338" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2338" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2338" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2338" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2338" s="3">
+        <v>41</v>
+      </c>
+      <c r="F2338" s="9">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2339" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2339" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2339" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2339" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2339" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2339" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2340" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2340" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2340" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2340" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2340" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2340" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2341" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2341" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2341" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2341" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2341" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2341" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2342" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2342" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2342" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2342" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2342" s="3">
+        <v>84</v>
+      </c>
+      <c r="F2342" s="9">
+        <v>0.82399999999999995</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2343" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2343" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2343" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2343" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2343" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2343" s="9">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2344" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2344" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2344" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2344" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2344" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2344" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2345" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2345" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2345" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2345" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2345" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2345" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2346" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2346" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2346" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2346" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2346" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2346" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2347" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2347" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2347" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2347" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2347" s="3">
+        <v>151</v>
+      </c>
+      <c r="F2347" s="9">
+        <v>0.91500000000000004</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2348" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2348" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2348" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2348" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2348" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2348" s="9">
+        <v>7.2999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2349" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2349" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2349" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2349" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2349" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2349" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2350" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2350" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2350" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2350" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2350" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2350" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2351" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2351" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2351" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2351" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2351" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2351" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2352" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2352" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2352" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2352" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2352" s="3">
+        <v>78</v>
+      </c>
+      <c r="F2352" s="9">
+        <v>0.90700000000000003</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2353" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2353" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2353" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2353" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2353" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2353" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2354" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2354" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2354" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2354" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2354" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2354" s="9">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2355" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2355" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2355" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2355" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2355" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2355" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2356" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2356" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2356" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2356" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2356" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2356" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE44447-9408-4C4B-B6AF-5D8A8C4EC206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6063BC-79B3-4038-8B50-3D53ED01166B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4932" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3091,6 +3091,29 @@
         <v>86</v>
       </c>
     </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2026</v>
+      </c>
+      <c r="B103" t="s">
+        <v>77</v>
+      </c>
+      <c r="C103">
+        <v>1228</v>
+      </c>
+      <c r="D103">
+        <v>860</v>
+      </c>
+      <c r="E103">
+        <v>136</v>
+      </c>
+      <c r="F103">
+        <v>220</v>
+      </c>
+      <c r="G103" s="17">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3099,7 +3122,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5369,6 +5392,29 @@
       </c>
       <c r="G102">
         <v>4.88</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>2026</v>
+      </c>
+      <c r="B103" t="s">
+        <v>77</v>
+      </c>
+      <c r="C103">
+        <v>4.91</v>
+      </c>
+      <c r="D103">
+        <v>4.91</v>
+      </c>
+      <c r="E103">
+        <v>4.74</v>
+      </c>
+      <c r="F103">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G103">
+        <v>4.83</v>
       </c>
     </row>
   </sheetData>
@@ -5379,7 +5425,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2356"/>
+  <dimension ref="A1:L2381"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -52550,6 +52596,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2357" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2357" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2357" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2357" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2357" s="3">
+        <v>1141</v>
+      </c>
+      <c r="F2357" s="9">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2358" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2358" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2358" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2358" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2358" s="3">
+        <v>71</v>
+      </c>
+      <c r="F2358" s="9">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2359" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2359" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2359" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2359" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2359" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2359" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2360" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2360" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2360" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2360" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2360" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2360" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2361" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2361" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2361" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2361" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2361" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2361" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2362" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2362" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2362" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2362" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2362" s="3">
+        <v>795</v>
+      </c>
+      <c r="F2362" s="9">
+        <v>0.92400000000000004</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2363" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2363" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2363" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2363" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2363" s="3">
+        <v>52</v>
+      </c>
+      <c r="F2363" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2364" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2364" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2364" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2364" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2364" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2364" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2365" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2365" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2365" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2365" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2365" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2365" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2366" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2366" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2366" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2366" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2366" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2366" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2367" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2367" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2367" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2367" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2367" s="3">
+        <v>110</v>
+      </c>
+      <c r="F2367" s="9">
+        <v>0.80900000000000005</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2368" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2368" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2368" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2368" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2368" s="3">
+        <v>19</v>
+      </c>
+      <c r="F2368" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2369" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2369" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2369" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2369" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2369" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2369" s="9">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2370" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2370" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2370" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2370" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2370" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2370" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2371" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2371" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2371" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2371" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2371" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2371" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2372" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2372" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2372" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2372" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2372" s="3">
+        <v>201</v>
+      </c>
+      <c r="F2372" s="9">
+        <v>0.91400000000000003</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2373" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2373" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2373" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2373" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2373" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2373" s="9">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2374" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2374" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2374" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2374" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2374" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2374" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2375" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2375" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2375" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2375" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2375" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2375" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2376" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2376" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2376" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2376" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2376" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2376" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2377" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2377" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2377" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2377" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2377" s="3">
+        <v>51</v>
+      </c>
+      <c r="F2377" s="9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2378" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2378" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2378" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2378" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2378" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2378" s="9">
+        <v>0.13300000000000001</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2379" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2379" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2379" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2379" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2379" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2379" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2380" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2380" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2380" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2380" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2380" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2380" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2381" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2381" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2381" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2381" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2381" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2381" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6063BC-79B3-4038-8B50-3D53ED01166B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0EE83B-6C3C-4B1D-AD1B-72396C9BC9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4984" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5036" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3114,6 +3114,29 @@
         <v>60</v>
       </c>
     </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2026</v>
+      </c>
+      <c r="B104" t="s">
+        <v>78</v>
+      </c>
+      <c r="C104">
+        <v>1315</v>
+      </c>
+      <c r="D104">
+        <v>674</v>
+      </c>
+      <c r="E104">
+        <v>111</v>
+      </c>
+      <c r="F104">
+        <v>187</v>
+      </c>
+      <c r="G104" s="17">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3122,7 +3145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5415,6 +5438,29 @@
       </c>
       <c r="G103">
         <v>4.83</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>2026</v>
+      </c>
+      <c r="B104" t="s">
+        <v>78</v>
+      </c>
+      <c r="C104">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D104">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E104">
+        <v>4.88</v>
+      </c>
+      <c r="F104">
+        <v>4.92</v>
+      </c>
+      <c r="G104">
+        <v>4.95</v>
       </c>
     </row>
   </sheetData>
@@ -5425,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2381"/>
+  <dimension ref="A1:L2406"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -53096,6 +53142,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2382" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2382" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2382" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2382" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2382" s="3">
+        <v>1203</v>
+      </c>
+      <c r="F2382" s="9">
+        <v>0.91500000000000004</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2383" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2383" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2383" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2383" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2383" s="3">
+        <v>91</v>
+      </c>
+      <c r="F2383" s="9">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2384" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2384" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2384" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2384" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2384" s="3">
+        <v>15</v>
+      </c>
+      <c r="F2384" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2385" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2385" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2385" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2385" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2385" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2385" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2386" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2386" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2386" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2386" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2386" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2386" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2387" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2387" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2387" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2387" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2387" s="3">
+        <v>621</v>
+      </c>
+      <c r="F2387" s="9">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2388" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2388" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2388" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2388" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2388" s="3">
+        <v>41</v>
+      </c>
+      <c r="F2388" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2389" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2389" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2389" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2389" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2389" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2389" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2390" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2390" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2390" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2390" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2390" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2390" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2391" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2391" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2391" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2391" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2391" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2391" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2392" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2392" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2392" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2392" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2392" s="3">
+        <v>100</v>
+      </c>
+      <c r="F2392" s="9">
+        <v>0.90100000000000002</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2393" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2393" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2393" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2393" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2393" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2393" s="9">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2394" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2394" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2394" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2394" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2394" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2394" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2395" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2395" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2395" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2395" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2395" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2395" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2396" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2396" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2396" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2396" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2396" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2396" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2397" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2397" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2397" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2397" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2397" s="3">
+        <v>172</v>
+      </c>
+      <c r="F2397" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2398" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2398" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2398" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2398" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2398" s="3">
+        <v>15</v>
+      </c>
+      <c r="F2398" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2399" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2399" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2399" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2399" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2399" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2399" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2400" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2400" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2400" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2400" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2400" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2400" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2401" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2401" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2401" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2401" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2401" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2401" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2402" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2402" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2402" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2402" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2402" s="3">
+        <v>80</v>
+      </c>
+      <c r="F2402" s="9">
+        <v>0.95199999999999996</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2403" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2403" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2403" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2403" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2403" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2403" s="9">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2404" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2404" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2404" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2404" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2404" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2404" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2405" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2405" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2405" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2405" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2405" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2405" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2406" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2406" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2406" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2406" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2406" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2406" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0EE83B-6C3C-4B1D-AD1B-72396C9BC9EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0163A6-8A77-4984-AB23-E25258C7994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5036" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5088" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3137,6 +3137,29 @@
         <v>84</v>
       </c>
     </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2026</v>
+      </c>
+      <c r="B105" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105">
+        <v>1299</v>
+      </c>
+      <c r="D105">
+        <v>801</v>
+      </c>
+      <c r="E105">
+        <v>115</v>
+      </c>
+      <c r="F105">
+        <v>193</v>
+      </c>
+      <c r="G105" s="17">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3145,7 +3168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5461,6 +5484,29 @@
       </c>
       <c r="G104">
         <v>4.95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>2026</v>
+      </c>
+      <c r="B105" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105">
+        <v>4.91</v>
+      </c>
+      <c r="D105">
+        <v>4.91</v>
+      </c>
+      <c r="E105">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F105">
+        <v>4.88</v>
+      </c>
+      <c r="G105">
+        <v>4.9400000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -5471,7 +5517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2406"/>
+  <dimension ref="A1:L2431"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -53642,6 +53688,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2407" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2407" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2407" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2407" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2407" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2407" s="3">
+        <v>1209</v>
+      </c>
+      <c r="F2407" s="9">
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2408" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2408" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2408" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2408" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2408" s="3">
+        <v>74</v>
+      </c>
+      <c r="F2408" s="9">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2409" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2409" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2409" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2409" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2409" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2409" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2410" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2410" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2410" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2410" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2410" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2410" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2411" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2411" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2411" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2411" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2411" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2411" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2412" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2412" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2412" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2412" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2412" s="3">
+        <v>736</v>
+      </c>
+      <c r="F2412" s="9">
+        <v>0.91900000000000004</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2413" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2413" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2413" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2413" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2413" s="3">
+        <v>58</v>
+      </c>
+      <c r="F2413" s="9">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2414" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2414" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2414" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2414" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2414" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2414" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2415" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2415" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2415" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2415" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2415" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2415" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2416" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2416" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2416" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2416" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2416" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2416" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2417" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2417" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2417" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2417" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2417" s="3">
+        <v>107</v>
+      </c>
+      <c r="F2417" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2418" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2418" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2418" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2418" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2418" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2418" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2419" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2419" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2419" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2419" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2419" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2419" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2420" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2420" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2420" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2420" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2420" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2420" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2421" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2421" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2421" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2421" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2421" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2421" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2422" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2422" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2422" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2422" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2422" s="3">
+        <v>175</v>
+      </c>
+      <c r="F2422" s="9">
+        <v>0.90700000000000003</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2423" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2423" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2423" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2423" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2423" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2423" s="9">
+        <v>7.2999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2424" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2424" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2424" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2424" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2424" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2424" s="9">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2425" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2425" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2425" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2425" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2425" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2425" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2426" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2426" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2426" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2426" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2426" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2426" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2427" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2427" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2427" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2427" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2427" s="3">
+        <v>82</v>
+      </c>
+      <c r="F2427" s="9">
+        <v>0.94299999999999995</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2428" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2428" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2428" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2428" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2428" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2428" s="9">
+        <v>5.7000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2429" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2429" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2429" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2429" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2429" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2429" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2430" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2430" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2430" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2430" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2430" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2430" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2431" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2431" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2431" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2431" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2431" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2431" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0163A6-8A77-4984-AB23-E25258C7994F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E558405-77AA-4E1D-9766-10B9E708F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5088" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5140" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3160,6 +3160,29 @@
         <v>87</v>
       </c>
     </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2026</v>
+      </c>
+      <c r="B106" t="s">
+        <v>80</v>
+      </c>
+      <c r="C106">
+        <v>1291</v>
+      </c>
+      <c r="D106">
+        <v>800</v>
+      </c>
+      <c r="E106">
+        <v>135</v>
+      </c>
+      <c r="F106">
+        <v>203</v>
+      </c>
+      <c r="G106" s="17">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3168,7 +3191,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5507,6 +5530,29 @@
       </c>
       <c r="G105">
         <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>2026</v>
+      </c>
+      <c r="B106" t="s">
+        <v>80</v>
+      </c>
+      <c r="C106">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D106">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E106">
+        <v>4.88</v>
+      </c>
+      <c r="F106">
+        <v>4.79</v>
+      </c>
+      <c r="G106">
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -5517,7 +5563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2431"/>
+  <dimension ref="A1:L2456"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -54188,6 +54234,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2432" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2432" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2432" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2432" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2432" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2432" s="3">
+        <v>1188</v>
+      </c>
+      <c r="F2432" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2433" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2433" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2433" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2433" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2433" s="3">
+        <v>83</v>
+      </c>
+      <c r="F2433" s="9">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2434" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2434" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2434" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2434" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2434" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2434" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2435" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2435" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2435" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2435" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2435" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2435" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2436" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2436" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2436" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2436" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2436" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2436" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2437" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2437" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2437" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2437" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2437" s="3">
+        <v>746</v>
+      </c>
+      <c r="F2437" s="9">
+        <v>0.93200000000000005</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2438" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2438" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2438" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2438" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2438" s="3">
+        <v>36</v>
+      </c>
+      <c r="F2438" s="9">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2439" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2439" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2439" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2439" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2439" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2439" s="9">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2440" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2440" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2440" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2440" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2440" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2440" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2441" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2441" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2441" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2441" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2441" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2441" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2442" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2442" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2442" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2442" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2442" s="3">
+        <v>120</v>
+      </c>
+      <c r="F2442" s="9">
+        <v>0.88900000000000001</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2443" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2443" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2443" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2443" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2443" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2443" s="9">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2444" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2444" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2444" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2444" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2444" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2444" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2445" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2445" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2445" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2445" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2445" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2445" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2446" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2446" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2446" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2446" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2446" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2446" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2447" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2447" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2447" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2447" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2447" s="3">
+        <v>176</v>
+      </c>
+      <c r="F2447" s="9">
+        <v>0.86699999999999999</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2448" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2448" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2448" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2448" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2448" s="3">
+        <v>17</v>
+      </c>
+      <c r="F2448" s="9">
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2449" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2449" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2449" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2449" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2449" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2449" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2450" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2450" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2450" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2450" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2450" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2450" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2451" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2451" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2451" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2451" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2451" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2451" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2452" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2452" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2452" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2452" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2452" s="3">
+        <v>59</v>
+      </c>
+      <c r="F2452" s="9">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2453" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2453" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2453" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2453" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2453" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2453" s="9">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2454" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2454" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2454" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2454" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2454" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2454" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2455" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2455" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2455" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2455" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2455" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2455" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2456" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2456" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2456" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2456" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2456" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2456" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E558405-77AA-4E1D-9766-10B9E708F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="13125" yWindow="0" windowWidth="19320" windowHeight="15480" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E558405-77AA-4E1D-9766-10B9E708F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C885F7A3-AC50-4EF0-8289-EE55F284F61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13125" yWindow="0" windowWidth="19320" windowHeight="15480" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5140" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5192" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3183,6 +3183,29 @@
         <v>66</v>
       </c>
     </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2026</v>
+      </c>
+      <c r="B107" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107">
+        <v>1329</v>
+      </c>
+      <c r="D107">
+        <v>783</v>
+      </c>
+      <c r="E107">
+        <v>139</v>
+      </c>
+      <c r="F107">
+        <v>182</v>
+      </c>
+      <c r="G107" s="17">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3191,7 +3214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5553,6 +5576,29 @@
       </c>
       <c r="G106">
         <v>4.88</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>2026</v>
+      </c>
+      <c r="B107" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107">
+        <v>4.91</v>
+      </c>
+      <c r="D107">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E107">
+        <v>4.78</v>
+      </c>
+      <c r="F107">
+        <v>4.88</v>
+      </c>
+      <c r="G107">
+        <v>4.87</v>
       </c>
     </row>
   </sheetData>
@@ -5563,7 +5609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2456"/>
+  <dimension ref="A1:L2481"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -54734,6 +54780,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2457" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2457" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2457" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2457" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2457" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2457" s="3">
+        <v>1236</v>
+      </c>
+      <c r="F2457" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2458" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2458" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2458" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2458" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2458" s="3">
+        <v>75</v>
+      </c>
+      <c r="F2458" s="9">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2459" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2459" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2459" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2459" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2459" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2459" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2460" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2460" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2460" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2460" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2460" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2460" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2461" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2461" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2461" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2461" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2461" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2461" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2462" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2462" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2462" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2462" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2462" s="3">
+        <v>722</v>
+      </c>
+      <c r="F2462" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2463" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2463" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2463" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2463" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2463" s="3">
+        <v>46</v>
+      </c>
+      <c r="F2463" s="9">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2464" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2464" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2464" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2464" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2464" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2464" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2465" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2465" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2465" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2465" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2465" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2465" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2466" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2466" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2466" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2466" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2466" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2466" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2467" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2467" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2467" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2467" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2467" s="3">
+        <v>111</v>
+      </c>
+      <c r="F2467" s="9">
+        <v>0.79900000000000004</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2468" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2468" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2468" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2468" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2468" s="3">
+        <v>25</v>
+      </c>
+      <c r="F2468" s="9">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2469" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2469" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2469" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2469" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2469" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2469" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2470" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2470" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2470" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2470" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2470" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2470" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2471" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2471" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2471" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2471" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2471" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2471" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2472" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2472" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2472" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2472" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2472" s="3">
+        <v>163</v>
+      </c>
+      <c r="F2472" s="9">
+        <v>0.89600000000000002</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2473" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2473" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2473" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2473" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2473" s="3">
+        <v>16</v>
+      </c>
+      <c r="F2473" s="9">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2474" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2474" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2474" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2474" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2474" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2474" s="9">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2475" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2475" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2475" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2475" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2475" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2475" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2476" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2476" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2476" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2476" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2476" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2476" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2477" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2477" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2477" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2477" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2477" s="3">
+        <v>93</v>
+      </c>
+      <c r="F2477" s="9">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2478" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2478" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2478" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2478" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2478" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2478" s="9">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2479" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2479" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2479" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2479" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2479" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2479" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2480" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2480" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2480" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2480" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2480" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2480" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2481" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2481" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2481" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2481" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2481" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2481" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C885F7A3-AC50-4EF0-8289-EE55F284F61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1515785-3948-4A3C-957D-80C2900196CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5192" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5244" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3206,6 +3206,29 @@
         <v>104</v>
       </c>
     </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2026</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>1235</v>
+      </c>
+      <c r="D108">
+        <v>859</v>
+      </c>
+      <c r="E108">
+        <v>110</v>
+      </c>
+      <c r="F108">
+        <v>222</v>
+      </c>
+      <c r="G108" s="17">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3214,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5599,6 +5622,29 @@
       </c>
       <c r="G107">
         <v>4.87</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>2026</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>4.91</v>
+      </c>
+      <c r="D108">
+        <v>4.91</v>
+      </c>
+      <c r="E108">
+        <v>4.83</v>
+      </c>
+      <c r="F108">
+        <v>4.88</v>
+      </c>
+      <c r="G108">
+        <v>4.79</v>
       </c>
     </row>
   </sheetData>
@@ -5609,7 +5655,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2481"/>
+  <dimension ref="A1:L2506"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -55280,6 +55326,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2482" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2482" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2482" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2482" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2482" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2482" s="3">
+        <v>1146</v>
+      </c>
+      <c r="F2482" s="9">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2483" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2483" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2483" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2483" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2483" s="3">
+        <v>73</v>
+      </c>
+      <c r="F2483" s="9">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2484" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2484" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2484" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2484" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2484" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2484" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2485" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2485" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2485" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2485" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2485" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2485" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2486" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2486" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2486" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2486" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2486" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2486" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2487" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2487" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2487" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2487" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2487" s="3">
+        <v>800</v>
+      </c>
+      <c r="F2487" s="9">
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2488" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2488" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2488" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2488" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2488" s="3">
+        <v>46</v>
+      </c>
+      <c r="F2488" s="9">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2489" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2489" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2489" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2489" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2489" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2489" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2490" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2490" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2490" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2490" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2490" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2490" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2491" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2491" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2491" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2491" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2491" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2491" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2492" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2492" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2492" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2492" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2492" s="3">
+        <v>93</v>
+      </c>
+      <c r="F2492" s="9">
+        <v>0.84499999999999997</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2493" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2493" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2493" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2493" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2493" s="3">
+        <v>15</v>
+      </c>
+      <c r="F2493" s="9">
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2494" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2494" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2494" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2494" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2494" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2494" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2495" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2495" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2495" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2495" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2495" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2495" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2496" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2496" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2496" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2496" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2496" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2496" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2497" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2497" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2497" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2497" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2497" s="3">
+        <v>200</v>
+      </c>
+      <c r="F2497" s="9">
+        <v>0.90100000000000002</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2498" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2498" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2498" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2498" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2498" s="3">
+        <v>18</v>
+      </c>
+      <c r="F2498" s="9">
+        <v>8.1000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2499" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2499" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2499" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2499" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2499" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2499" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2500" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2500" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2500" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2500" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2500" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2500" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2501" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2501" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2501" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2501" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2501" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2501" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2502" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2502" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2502" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2502" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2502" s="3">
+        <v>88</v>
+      </c>
+      <c r="F2502" s="9">
+        <v>0.86299999999999999</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2503" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2503" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2503" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2503" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2503" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2503" s="9">
+        <v>9.8000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2504" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2504" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2504" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2504" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2504" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2504" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2505" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2505" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2505" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2505" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2505" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2505" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2506" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2506" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2506" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2506" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2506" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2506" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1515785-3948-4A3C-957D-80C2900196CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A7921-D0A5-4679-934C-3A1C9F8596E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5244" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5296" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3229,6 +3229,29 @@
         <v>102</v>
       </c>
     </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2026</v>
+      </c>
+      <c r="B109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109">
+        <v>1181</v>
+      </c>
+      <c r="D109">
+        <v>768</v>
+      </c>
+      <c r="E109">
+        <v>109</v>
+      </c>
+      <c r="F109">
+        <v>191</v>
+      </c>
+      <c r="G109" s="17">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3237,7 +3260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5645,6 +5668,29 @@
       </c>
       <c r="G108">
         <v>4.79</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>2026</v>
+      </c>
+      <c r="B109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D109">
+        <v>4.88</v>
+      </c>
+      <c r="E109">
+        <v>4.83</v>
+      </c>
+      <c r="F109">
+        <v>4.87</v>
+      </c>
+      <c r="G109">
+        <v>4.8899999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2506"/>
+  <dimension ref="A1:L2531"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -55826,6 +55872,506 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="2507" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2507" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2507" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2507" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2507" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2507" s="3">
+        <v>1089</v>
+      </c>
+      <c r="F2507" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2508" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2508" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2508" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2508" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2508" s="3">
+        <v>72</v>
+      </c>
+      <c r="F2508" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2509" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2509" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2509" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2509" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2509" s="3">
+        <v>17</v>
+      </c>
+      <c r="F2509" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2510" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2510" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2510" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2510" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2510" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2510" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2511" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2511" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2511" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2511" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2511" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2511" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2512" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2512" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2512" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2512" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2512" s="3">
+        <v>702</v>
+      </c>
+      <c r="F2512" s="9">
+        <v>0.91400000000000003</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2513" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2513" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2513" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2513" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2513" s="3">
+        <v>47</v>
+      </c>
+      <c r="F2513" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2514" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2514" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2514" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2514" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2514" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2514" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2515" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2515" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2515" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2515" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2515" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2515" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2516" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2516" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2516" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2516" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2516" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2516" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2517" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2517" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2517" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2517" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2517" s="3">
+        <v>94</v>
+      </c>
+      <c r="F2517" s="9">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2518" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2518" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2518" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2518" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2518" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2518" s="9">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2519" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2519" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2519" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2519" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2519" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2519" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2520" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2520" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2520" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2520" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2520" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2520" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2521" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2521" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2521" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2521" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2521" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2521" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2522" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2522" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2522" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2522" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2522" s="3">
+        <v>174</v>
+      </c>
+      <c r="F2522" s="9">
+        <v>0.91100000000000003</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2523" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2523" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2523" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2523" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2523" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2523" s="9">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2524" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2524" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2524" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2524" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2524" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2524" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2525" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2525" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2525" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2525" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2525" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2525" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2526" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2526" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2526" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2526" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2526" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2526" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2527" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2527" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2527" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2527" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2527" s="3">
+        <v>92</v>
+      </c>
+      <c r="F2527" s="9">
+        <v>0.90200000000000002</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2528" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2528" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2528" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2528" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2528" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2528" s="9">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2529" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2529" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2529" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2529" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2529" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2529" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2530" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2530" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2530" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2530" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2530" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2530" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2531" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2531" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2531" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2531" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2531" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2531" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A7921-D0A5-4679-934C-3A1C9F8596E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD2E59E-083F-4172-9C9B-8BC76153F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5296" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5348" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3252,6 +3252,29 @@
         <v>102</v>
       </c>
     </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2026</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110">
+        <v>999</v>
+      </c>
+      <c r="D110">
+        <v>591</v>
+      </c>
+      <c r="E110">
+        <v>94</v>
+      </c>
+      <c r="F110">
+        <v>153</v>
+      </c>
+      <c r="G110" s="17">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3260,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5691,6 +5714,29 @@
       </c>
       <c r="G109">
         <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>2026</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110">
+        <v>4.92</v>
+      </c>
+      <c r="D110">
+        <v>4.91</v>
+      </c>
+      <c r="E110">
+        <v>4.87</v>
+      </c>
+      <c r="F110">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G110">
+        <v>4.92</v>
       </c>
     </row>
   </sheetData>
@@ -5701,7 +5747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2531"/>
+  <dimension ref="A1:L2556"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -56372,6 +56418,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2532" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2532" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2532" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2532" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2532" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2532" s="3">
+        <v>927</v>
+      </c>
+      <c r="F2532" s="9">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2533" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2533" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2533" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2533" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2533" s="3">
+        <v>62</v>
+      </c>
+      <c r="F2533" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2534" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2534" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2534" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2534" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2534" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2534" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2535" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2535" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2535" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2535" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2535" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2535" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2536" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2536" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2536" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2536" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2536" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2536" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2537" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2537" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2537" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2537" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2537" s="3">
+        <v>552</v>
+      </c>
+      <c r="F2537" s="9">
+        <v>0.93400000000000005</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2538" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2538" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2538" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2538" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2538" s="3">
+        <v>29</v>
+      </c>
+      <c r="F2538" s="9">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2539" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2539" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2539" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2539" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2539" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2539" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2540" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2540" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2540" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2540" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2540" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2540" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2541" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2541" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2541" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2541" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2541" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2541" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2542" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2542" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2542" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2542" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2542" s="3">
+        <v>83</v>
+      </c>
+      <c r="F2542" s="9">
+        <v>0.88300000000000001</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2543" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2543" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2543" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2543" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2543" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2543" s="9">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2544" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2544" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2544" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2544" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2544" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2544" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2545" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2545" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2545" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2545" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2545" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2545" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2546" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2546" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2546" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2546" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2546" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2546" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2547" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2547" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2547" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2547" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2547" s="3">
+        <v>142</v>
+      </c>
+      <c r="F2547" s="9">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2548" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2548" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2548" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2548" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2548" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2548" s="9">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2549" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2549" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2549" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2549" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2549" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2549" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2550" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2550" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2550" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2550" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2550" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2550" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2551" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2551" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2551" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2551" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2551" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2551" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2552" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2552" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2552" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2552" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2552" s="3">
+        <v>79</v>
+      </c>
+      <c r="F2552" s="9">
+        <v>0.95199999999999996</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2553" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2553" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2553" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2553" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2553" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2553" s="9">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2554" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2554" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2554" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2554" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2554" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2554" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2555" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2555" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2555" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2555" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2555" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2555" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2556" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2556" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2556" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2556" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2556" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2556" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD2E59E-083F-4172-9C9B-8BC76153F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D20426-1688-4074-B087-01C9DCE00F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5348" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5400" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3275,6 +3275,29 @@
         <v>83</v>
       </c>
     </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>2026</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111">
+        <v>1119</v>
+      </c>
+      <c r="D111">
+        <v>640</v>
+      </c>
+      <c r="E111">
+        <v>97</v>
+      </c>
+      <c r="F111">
+        <v>205</v>
+      </c>
+      <c r="G111" s="17">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3283,7 +3306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5737,6 +5760,29 @@
       </c>
       <c r="G110">
         <v>4.92</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>2026</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111">
+        <v>4.92</v>
+      </c>
+      <c r="D111">
+        <v>4.91</v>
+      </c>
+      <c r="E111">
+        <v>4.78</v>
+      </c>
+      <c r="F111">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="G111">
+        <v>4.72</v>
       </c>
     </row>
   </sheetData>
@@ -5747,7 +5793,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2556"/>
+  <dimension ref="A1:L2581"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -56918,6 +56964,506 @@
         <v>1.2E-2</v>
       </c>
     </row>
+    <row r="2557" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2557" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2557" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2557" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2557" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2557" s="3">
+        <v>1046</v>
+      </c>
+      <c r="F2557" s="9">
+        <v>0.93500000000000005</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2558" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2558" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2558" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2558" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2558" s="3">
+        <v>62</v>
+      </c>
+      <c r="F2558" s="9">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2559" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2559" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2559" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2559" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2559" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2559" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2560" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2560" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2560" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2560" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2560" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2560" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2561" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2561" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2561" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2561" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2561" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2561" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2562" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2562" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2562" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2562" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2562" s="3">
+        <v>590</v>
+      </c>
+      <c r="F2562" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2563" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2563" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2563" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2563" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2563" s="3">
+        <v>40</v>
+      </c>
+      <c r="F2563" s="9">
+        <v>6.2E-2</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2564" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2564" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2564" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2564" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2564" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2564" s="9">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2565" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2565" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2565" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2565" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2565" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2565" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2566" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2566" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2566" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2566" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2566" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2566" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2567" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2567" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2567" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2567" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2567" s="3">
+        <v>82</v>
+      </c>
+      <c r="F2567" s="9">
+        <v>0.84499999999999997</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2568" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2568" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2568" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2568" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2568" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2568" s="9">
+        <v>0.10299999999999999</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2569" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2569" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2569" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2569" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2569" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2569" s="9">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2570" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2570" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2570" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2570" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2570" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2570" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2571" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2571" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2571" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2571" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2571" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2571" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2572" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2572" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2572" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2572" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2572" s="3">
+        <v>187</v>
+      </c>
+      <c r="F2572" s="9">
+        <v>0.91200000000000003</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2573" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2573" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2573" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2573" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2573" s="3">
+        <v>15</v>
+      </c>
+      <c r="F2573" s="9">
+        <v>7.2999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2574" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2574" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2574" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2574" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2574" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2574" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2575" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2575" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2575" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2575" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2575" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2575" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2576" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2576" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2576" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2576" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2576" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2576" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2577" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2577" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2577" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2577" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2577" s="3">
+        <v>70</v>
+      </c>
+      <c r="F2577" s="9">
+        <v>0.85399999999999998</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2578" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2578" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2578" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2578" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2578" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2578" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2579" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2579" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2579" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2579" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2579" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2579" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2580" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2580" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2580" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2580" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2580" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2580" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2581" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2581" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2581" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2581" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2581" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2581" s="9">
+        <v>2.4E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D20426-1688-4074-B087-01C9DCE00F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4143038F-8B0A-429A-AD97-FCFD4C08E1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5400" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5452" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3298,6 +3298,29 @@
         <v>82</v>
       </c>
     </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2026</v>
+      </c>
+      <c r="B112" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112">
+        <v>1034</v>
+      </c>
+      <c r="D112">
+        <v>662</v>
+      </c>
+      <c r="E112">
+        <v>120</v>
+      </c>
+      <c r="F112">
+        <v>201</v>
+      </c>
+      <c r="G112" s="17">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3306,7 +3329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5783,6 +5806,29 @@
       </c>
       <c r="G111">
         <v>4.72</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>2026</v>
+      </c>
+      <c r="B112" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112">
+        <v>4.91</v>
+      </c>
+      <c r="D112">
+        <v>4.91</v>
+      </c>
+      <c r="E112">
+        <v>4.82</v>
+      </c>
+      <c r="F112">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G112">
+        <v>4.91</v>
       </c>
     </row>
   </sheetData>
@@ -5793,7 +5839,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2581"/>
+  <dimension ref="A1:L2606"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -57464,6 +57510,506 @@
         <v>2.4E-2</v>
       </c>
     </row>
+    <row r="2582" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2582" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2582" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2582" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2582" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2582" s="3">
+        <v>953</v>
+      </c>
+      <c r="F2582" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2583" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2583" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2583" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2583" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2583" s="3">
+        <v>74</v>
+      </c>
+      <c r="F2583" s="9">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2584" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2584" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2584" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2584" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2584" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2584" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2585" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2585" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2585" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2585" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2585" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2585" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2586" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2586" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2586" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2586" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2586" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2586" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2587" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2587" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2587" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2587" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2587" s="3">
+        <v>615</v>
+      </c>
+      <c r="F2587" s="9">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2588" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2588" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2588" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2588" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2588" s="3">
+        <v>37</v>
+      </c>
+      <c r="F2588" s="9">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2589" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2589" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2589" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2589" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2589" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2589" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2590" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2590" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2590" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2590" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2590" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2590" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2591" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2591" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2591" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2591" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2591" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2591" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2592" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2592" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2592" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2592" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2592" s="3">
+        <v>104</v>
+      </c>
+      <c r="F2592" s="9">
+        <v>0.86699999999999999</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2593" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2593" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2593" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2593" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2593" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2593" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2594" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2594" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2594" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2594" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2594" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2594" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2595" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2595" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2595" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2595" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2595" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2595" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2596" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2596" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2596" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2596" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2596" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2596" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2597" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2597" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2597" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2597" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2597" s="3">
+        <v>183</v>
+      </c>
+      <c r="F2597" s="9">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2598" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2598" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2598" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2598" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2598" s="3">
+        <v>16</v>
+      </c>
+      <c r="F2598" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2599" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2599" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2599" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2599" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2599" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2599" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2600" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2600" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2600" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2600" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2600" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2600" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2601" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2601" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2601" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2601" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2601" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2601" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2602" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2602" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2602" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2602" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2602" s="3">
+        <v>114</v>
+      </c>
+      <c r="F2602" s="9">
+        <v>0.95799999999999996</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2603" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2603" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2603" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2603" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2603" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2603" s="9">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2604" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2604" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2604" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2604" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2604" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2604" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2605" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2605" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2605" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2605" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2605" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2605" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2606" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2606" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2606" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2606" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2606" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2606" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4143038F-8B0A-429A-AD97-FCFD4C08E1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B815EE39-9F6C-46E8-836C-B173CA2A9CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5452" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5504" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3321,6 +3321,29 @@
         <v>119</v>
       </c>
     </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>2026</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113">
+        <v>968</v>
+      </c>
+      <c r="D113">
+        <v>627</v>
+      </c>
+      <c r="E113">
+        <v>105</v>
+      </c>
+      <c r="F113">
+        <v>170</v>
+      </c>
+      <c r="G113" s="17">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3329,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5829,6 +5852,29 @@
       </c>
       <c r="G112">
         <v>4.91</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>2026</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D113">
+        <v>4.92</v>
+      </c>
+      <c r="E113">
+        <v>4.74</v>
+      </c>
+      <c r="F113">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="G113">
+        <v>4.87</v>
       </c>
     </row>
   </sheetData>
@@ -5839,7 +5885,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2606"/>
+  <dimension ref="A1:L2631"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -58010,6 +58056,506 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
+    <row r="2607" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2607" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2607" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2607" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2607" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2607" s="3">
+        <v>895</v>
+      </c>
+      <c r="F2607" s="9">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2608" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2608" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2608" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2608" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2608" s="3">
+        <v>57</v>
+      </c>
+      <c r="F2608" s="9">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2609" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2609" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2609" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2609" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2609" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2609" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2610" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2610" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2610" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2610" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2610" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2610" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2611" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2611" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2611" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2611" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2611" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2611" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2612" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2612" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2612" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2612" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2612" s="3">
+        <v>584</v>
+      </c>
+      <c r="F2612" s="9">
+        <v>0.93100000000000005</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2613" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2613" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2613" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2613" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2613" s="3">
+        <v>34</v>
+      </c>
+      <c r="F2613" s="9">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2614" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2614" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2614" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2614" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2614" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2614" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2615" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2615" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2615" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2615" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2615" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2615" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2616" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2616" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2616" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2616" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2616" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2616" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2617" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2617" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2617" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2617" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2617" s="3">
+        <v>84</v>
+      </c>
+      <c r="F2617" s="9">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2618" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2618" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2618" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2618" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2618" s="3">
+        <v>16</v>
+      </c>
+      <c r="F2618" s="9">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2619" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2619" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2619" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2619" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2619" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2619" s="9">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2620" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2620" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2620" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2620" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2620" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2620" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2621" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2621" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2621" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2621" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2621" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2621" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2622" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2622" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2622" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2622" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2622" s="3">
+        <v>156</v>
+      </c>
+      <c r="F2622" s="9">
+        <v>0.91800000000000004</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2623" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2623" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2623" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2623" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2623" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2623" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2624" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2624" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2624" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2624" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2624" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2624" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2625" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2625" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2625" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2625" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2625" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2625" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2626" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2626" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2626" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2626" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2626" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2626" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2627" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2627" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2627" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2627" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2627" s="3">
+        <v>80</v>
+      </c>
+      <c r="F2627" s="9">
+        <v>0.89900000000000002</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2628" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2628" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2628" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2628" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2628" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2628" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2629" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2629" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2629" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2629" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2629" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2629" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2630" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2630" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2630" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2630" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2630" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2630" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2631" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2631" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2631" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2631" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2631" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2631" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B815EE39-9F6C-46E8-836C-B173CA2A9CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B599F77F-99D1-47E0-A70D-7496DD133233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5504" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5556" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3344,6 +3344,29 @@
         <v>89</v>
       </c>
     </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>2026</v>
+      </c>
+      <c r="B114" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114">
+        <v>940</v>
+      </c>
+      <c r="D114">
+        <v>601</v>
+      </c>
+      <c r="E114">
+        <v>71</v>
+      </c>
+      <c r="F114">
+        <v>173</v>
+      </c>
+      <c r="G114" s="17">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3352,7 +3375,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5875,6 +5898,29 @@
       </c>
       <c r="G113">
         <v>4.87</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>2026</v>
+      </c>
+      <c r="B114" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114">
+        <v>4.88</v>
+      </c>
+      <c r="D114">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E114">
+        <v>4.8</v>
+      </c>
+      <c r="F114">
+        <v>4.88</v>
+      </c>
+      <c r="G114">
+        <v>4.84</v>
       </c>
     </row>
   </sheetData>
@@ -5885,7 +5931,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2631"/>
+  <dimension ref="A1:L2656"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -58556,6 +58602,506 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
+    <row r="2632" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2632" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2632" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2632" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2632" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2632" s="3">
+        <v>855</v>
+      </c>
+      <c r="F2632" s="9">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2633" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2633" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2633" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2633" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2633" s="3">
+        <v>64</v>
+      </c>
+      <c r="F2633" s="9">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2634" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2634" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2634" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2634" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2634" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2634" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2635" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2635" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2635" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2635" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2635" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2635" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2636" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2636" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2636" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2636" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2636" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2636" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2637" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2637" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2637" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2637" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2637" s="3">
+        <v>551</v>
+      </c>
+      <c r="F2637" s="9">
+        <v>0.91700000000000004</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2638" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2638" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2638" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2638" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2638" s="3">
+        <v>39</v>
+      </c>
+      <c r="F2638" s="9">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2639" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2639" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2639" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2639" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2639" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2639" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2640" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2640" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2640" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2640" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2640" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2640" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2641" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2641" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2641" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2641" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2641" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2641" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2642" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2642" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2642" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2642" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2642" s="3">
+        <v>63</v>
+      </c>
+      <c r="F2642" s="9">
+        <v>0.88700000000000001</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2643" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2643" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2643" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2643" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2643" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2643" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2644" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2644" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2644" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2644" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2644" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2644" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2645" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2645" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2645" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2645" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2645" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2645" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2646" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2646" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2646" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2646" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2646" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2646" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2647" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2647" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2647" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2647" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2647" s="3">
+        <v>157</v>
+      </c>
+      <c r="F2647" s="9">
+        <v>0.90800000000000003</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2648" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2648" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2648" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2648" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2648" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2648" s="9">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2649" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2649" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2649" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2649" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2649" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2649" s="9">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2650" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2650" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2650" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2650" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2650" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2650" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2651" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2651" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2651" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2651" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2651" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2651" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2652" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2652" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2652" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2652" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2652" s="3">
+        <v>62</v>
+      </c>
+      <c r="F2652" s="9">
+        <v>0.89900000000000002</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2653" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2653" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2653" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2653" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2653" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2653" s="9">
+        <v>7.1999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2654" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2654" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2654" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2654" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2654" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2654" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2655" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2655" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2655" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2655" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2655" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2655" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2656" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2656" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2656" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2656" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2656" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2656" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B599F77F-99D1-47E0-A70D-7496DD133233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCA2A23-7CAA-4B7A-8BB7-08AF8C548914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5556" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5608" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3367,6 +3367,29 @@
         <v>69</v>
       </c>
     </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>2026</v>
+      </c>
+      <c r="B115" t="s">
+        <v>33</v>
+      </c>
+      <c r="C115">
+        <v>988</v>
+      </c>
+      <c r="D115">
+        <v>585</v>
+      </c>
+      <c r="E115">
+        <v>115</v>
+      </c>
+      <c r="F115">
+        <v>137</v>
+      </c>
+      <c r="G115" s="17">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3375,7 +3398,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5921,6 +5944,29 @@
       </c>
       <c r="G114">
         <v>4.84</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>2026</v>
+      </c>
+      <c r="B115" t="s">
+        <v>33</v>
+      </c>
+      <c r="C115">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D115">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="E115">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="F115">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G115">
+        <v>4.96</v>
       </c>
     </row>
   </sheetData>
@@ -5931,7 +5977,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2656"/>
+  <dimension ref="A1:L2681"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -59102,6 +59148,506 @@
         <v>1.4E-2</v>
       </c>
     </row>
+    <row r="2657" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2657" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2657" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2657" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2657" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2657" s="3">
+        <v>899</v>
+      </c>
+      <c r="F2657" s="9">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2658" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2658" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2658" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2658" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2658" s="3">
+        <v>74</v>
+      </c>
+      <c r="F2658" s="9">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2659" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2659" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2659" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2659" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2659" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2659" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2660" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2660" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2660" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2660" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2660" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2660" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2661" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2661" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2661" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2661" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2661" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2661" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2662" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2662" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2662" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2662" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2662" s="3">
+        <v>533</v>
+      </c>
+      <c r="F2662" s="9">
+        <v>0.91100000000000003</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2663" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2663" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2663" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2663" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2663" s="3">
+        <v>41</v>
+      </c>
+      <c r="F2663" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2664" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2664" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2664" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2664" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2664" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2664" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2665" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2665" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2665" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2665" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2665" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2666" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2666" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2666" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2666" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2666" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2666" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2667" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2667" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2667" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2667" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2667" s="3">
+        <v>101</v>
+      </c>
+      <c r="F2667" s="9">
+        <v>0.878</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2668" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2668" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2668" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2668" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2668" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2668" s="9">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2669" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2669" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2669" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2669" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2669" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2669" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2670" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2670" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2670" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2670" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2670" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2670" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2671" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2671" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2671" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2671" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2671" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2671" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2672" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2672" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2672" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2672" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2672" s="3">
+        <v>122</v>
+      </c>
+      <c r="F2672" s="9">
+        <v>0.89100000000000001</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2673" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2673" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2673" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2673" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2673" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2673" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2674" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2674" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2674" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2674" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2674" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2674" s="9">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2675" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2675" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2675" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2675" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2675" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2675" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2676" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2676" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2676" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2676" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2676" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2676" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2677" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2677" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2677" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2677" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2677" s="3">
+        <v>79</v>
+      </c>
+      <c r="F2677" s="9">
+        <v>0.96299999999999997</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2678" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2678" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2678" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2678" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2678" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2678" s="9">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2679" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2679" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2679" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2679" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2679" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2680" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2680" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2680" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2680" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2680" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2681" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2681" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2681" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2681" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2681" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2681" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCA2A23-7CAA-4B7A-8BB7-08AF8C548914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D74E81E-137C-466C-91C7-5DC5F51274A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5608" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5660" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3390,6 +3390,29 @@
         <v>82</v>
       </c>
     </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>2026</v>
+      </c>
+      <c r="B116" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116">
+        <v>1002</v>
+      </c>
+      <c r="D116">
+        <v>729</v>
+      </c>
+      <c r="E116">
+        <v>86</v>
+      </c>
+      <c r="F116">
+        <v>160</v>
+      </c>
+      <c r="G116" s="17">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3398,7 +3421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -5967,6 +5990,29 @@
       </c>
       <c r="G115">
         <v>4.96</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>2026</v>
+      </c>
+      <c r="B116" t="s">
+        <v>34</v>
+      </c>
+      <c r="C116">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D116">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E116">
+        <v>4.84</v>
+      </c>
+      <c r="F116">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="G116">
+        <v>4.92</v>
       </c>
     </row>
   </sheetData>
@@ -5977,7 +6023,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2681"/>
+  <dimension ref="A1:L2706"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -59648,6 +59694,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2682" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2682" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2682" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2682" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2682" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2682" s="3">
+        <v>921</v>
+      </c>
+      <c r="F2682" s="9">
+        <v>0.91900000000000004</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2683" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2683" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2683" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2683" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2683" s="3">
+        <v>63</v>
+      </c>
+      <c r="F2683" s="9">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2684" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2684" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2684" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2684" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2684" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2684" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2685" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2685" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2685" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2685" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2685" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2685" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2686" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2686" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2686" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2686" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2686" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2686" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2687" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2687" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2687" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2687" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2687" s="3">
+        <v>672</v>
+      </c>
+      <c r="F2687" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2688" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2688" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2688" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2688" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2688" s="3">
+        <v>49</v>
+      </c>
+      <c r="F2688" s="9">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2689" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2689" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2689" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2689" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2689" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2689" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2690" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2690" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2690" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2690" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2690" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2690" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2690" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2691" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2691" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2691" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2691" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2691" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2691" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2691" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2692" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2692" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2692" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2692" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2692" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2692" s="3">
+        <v>76</v>
+      </c>
+      <c r="F2692" s="9">
+        <v>0.88400000000000001</v>
+      </c>
+    </row>
+    <row r="2693" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2693" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2693" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2693" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2693" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2693" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2693" s="9">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2694" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2694" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2694" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2694" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2694" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2694" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2694" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2695" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2695" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2695" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2695" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2695" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2695" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2696" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2696" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2696" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2696" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2696" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2696" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2697" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2697" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2697" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2697" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2697" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2697" s="3">
+        <v>143</v>
+      </c>
+      <c r="F2697" s="9">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="2698" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2698" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2698" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2698" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2698" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2698" s="3">
+        <v>15</v>
+      </c>
+      <c r="F2698" s="9">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="2699" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2699" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2699" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2699" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2699" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2699" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2699" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2700" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2700" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2700" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2700" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2700" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2700" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2700" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2701" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2701" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2701" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2701" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2701" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2701" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2701" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2702" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2702" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2702" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2702" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2702" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2702" s="3">
+        <v>92</v>
+      </c>
+      <c r="F2702" s="9">
+        <v>0.93899999999999995</v>
+      </c>
+    </row>
+    <row r="2703" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2703" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2703" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2703" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2703" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2703" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2703" s="9">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2704" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2704" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2704" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2704" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2704" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2704" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2704" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2705" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2705" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2705" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2705" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2705" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2705" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2706" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2706" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2706" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2706" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2706" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2706" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2706" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D74E81E-137C-466C-91C7-5DC5F51274A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEE747E-8290-46B2-89EE-D12AC1D87D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5660" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5712" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3413,6 +3413,29 @@
         <v>98</v>
       </c>
     </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>2026</v>
+      </c>
+      <c r="B117" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117">
+        <v>946</v>
+      </c>
+      <c r="D117">
+        <v>622</v>
+      </c>
+      <c r="E117">
+        <v>85</v>
+      </c>
+      <c r="F117">
+        <v>168</v>
+      </c>
+      <c r="G117" s="17">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3421,7 +3444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6013,6 +6036,29 @@
       </c>
       <c r="G116">
         <v>4.92</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>2026</v>
+      </c>
+      <c r="B117" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117">
+        <v>4.91</v>
+      </c>
+      <c r="D117">
+        <v>4.88</v>
+      </c>
+      <c r="E117">
+        <v>4.91</v>
+      </c>
+      <c r="F117">
+        <v>4.92</v>
+      </c>
+      <c r="G117">
+        <v>4.87</v>
       </c>
     </row>
   </sheetData>
@@ -6023,7 +6069,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2706"/>
+  <dimension ref="A1:L2731"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -60194,6 +60240,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2707" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2707" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2707" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2707" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2707" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2707" s="3">
+        <v>877</v>
+      </c>
+      <c r="F2707" s="9">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="2708" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2708" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2708" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2708" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2708" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2708" s="3">
+        <v>56</v>
+      </c>
+      <c r="F2708" s="9">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2709" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2709" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2709" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2709" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2709" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2709" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2710" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2710" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2710" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2710" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2710" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2710" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2711" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2711" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2711" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2711" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2711" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2711" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2712" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2712" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2712" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2712" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2712" s="3">
+        <v>570</v>
+      </c>
+      <c r="F2712" s="9">
+        <v>0.91600000000000004</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2713" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2713" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2713" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2713" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2713" s="3">
+        <v>38</v>
+      </c>
+      <c r="F2713" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2714" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2714" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2714" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2714" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2714" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2714" s="9">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2715" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2715" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2715" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2715" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2715" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2715" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2716" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2716" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2716" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2716" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2716" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2716" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2717" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2717" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2717" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2717" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2717" s="3">
+        <v>78</v>
+      </c>
+      <c r="F2717" s="9">
+        <v>0.91800000000000004</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2718" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2718" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2718" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2718" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2718" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2718" s="9">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2719" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2719" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2719" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2719" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2719" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2719" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2720" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2720" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2720" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2720" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2720" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2721" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2721" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2721" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2721" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2721" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2721" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2722" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2722" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2722" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2722" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2722" s="3">
+        <v>155</v>
+      </c>
+      <c r="F2722" s="9">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2723" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2723" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2723" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2723" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2723" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2723" s="9">
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2724" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2724" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2724" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2724" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2724" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2724" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2725" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2725" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2725" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2725" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2725" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2725" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2725" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2726" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2726" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2726" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2726" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2726" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2726" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2726" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2727" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2727" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2727" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2727" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2727" s="3">
+        <v>81</v>
+      </c>
+      <c r="F2727" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2728" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2728" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2728" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2728" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2728" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2728" s="9">
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="2729" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2729" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2729" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2729" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2729" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2729" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2729" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2730" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2730" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2730" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2730" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2730" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2730" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2731" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2731" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2731" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2731" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2731" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2731" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEE747E-8290-46B2-89EE-D12AC1D87D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947BDD04-8A9B-4FBB-A99C-FA9248115008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5712" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5764" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3436,6 +3436,29 @@
         <v>91</v>
       </c>
     </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>2026</v>
+      </c>
+      <c r="B118" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118">
+        <v>859</v>
+      </c>
+      <c r="D118">
+        <v>619</v>
+      </c>
+      <c r="E118">
+        <v>94</v>
+      </c>
+      <c r="F118">
+        <v>184</v>
+      </c>
+      <c r="G118" s="17">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3444,7 +3467,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6059,6 +6082,29 @@
       </c>
       <c r="G117">
         <v>4.87</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>2026</v>
+      </c>
+      <c r="B118" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D118">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E118">
+        <v>4.87</v>
+      </c>
+      <c r="F118">
+        <v>4.93</v>
+      </c>
+      <c r="G118">
+        <v>4.8600000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -6069,7 +6115,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2731"/>
+  <dimension ref="A1:L2756"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -60740,6 +60786,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2732" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2732" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2732" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2732" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2732" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2732" s="3">
+        <v>784</v>
+      </c>
+      <c r="F2732" s="9">
+        <v>0.91300000000000003</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2733" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2733" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2733" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2733" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2733" s="3">
+        <v>60</v>
+      </c>
+      <c r="F2733" s="9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2734" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2734" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2734" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2734" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2734" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2734" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2735" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2735" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2735" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2735" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2735" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2735" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2735" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2736" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2736" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2736" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2736" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2736" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2736" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2736" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2737" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2737" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2737" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2737" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2737" s="3">
+        <v>577</v>
+      </c>
+      <c r="F2737" s="9">
+        <v>0.93200000000000005</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2738" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2738" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2738" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2738" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2738" s="3">
+        <v>28</v>
+      </c>
+      <c r="F2738" s="9">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2739" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2739" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2739" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2739" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2739" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2739" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2739" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2740" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2740" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2740" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2740" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2740" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2740" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2741" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2741" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2741" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2741" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2741" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2741" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2742" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2742" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2742" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2742" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2742" s="3">
+        <v>84</v>
+      </c>
+      <c r="F2742" s="9">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2743" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2743" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2743" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2743" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2743" s="9">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2744" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2744" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2744" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2744" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2744" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2744" s="9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2745" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2745" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2745" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2745" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2745" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2745" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2746" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2746" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2746" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2746" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2746" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2746" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2747" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2747" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2747" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2747" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2747" s="3">
+        <v>173</v>
+      </c>
+      <c r="F2747" s="9">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2748" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2748" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2748" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2748" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2748" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2748" s="9">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2749" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2749" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2749" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2749" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2749" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2749" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2750" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2750" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2750" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2750" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2750" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2750" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2751" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2751" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2751" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2751" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2751" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2751" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2752" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2752" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2752" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2752" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2752" s="3">
+        <v>65</v>
+      </c>
+      <c r="F2752" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="2753" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2753" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2753" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2753" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2753" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2753" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2753" s="9">
+        <v>8.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2754" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2754" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2754" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2754" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2754" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2754" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2754" s="9">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="2755" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2755" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2755" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2755" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2755" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2755" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2755" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2756" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2756" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2756" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2756" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2756" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2756" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2756" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947BDD04-8A9B-4FBB-A99C-FA9248115008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B668A2F-7FC6-4F6B-B244-75B4EFBDBDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5764" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5816" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3459,6 +3459,29 @@
         <v>73</v>
       </c>
     </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>2026</v>
+      </c>
+      <c r="B119" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119">
+        <v>1014</v>
+      </c>
+      <c r="D119">
+        <v>638</v>
+      </c>
+      <c r="E119">
+        <v>95</v>
+      </c>
+      <c r="F119">
+        <v>179</v>
+      </c>
+      <c r="G119" s="17">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3467,7 +3490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6105,6 +6128,29 @@
       </c>
       <c r="G118">
         <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>2026</v>
+      </c>
+      <c r="B119" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D119">
+        <v>4.87</v>
+      </c>
+      <c r="E119">
+        <v>4.8</v>
+      </c>
+      <c r="F119">
+        <v>4.87</v>
+      </c>
+      <c r="G119">
+        <v>4.96</v>
       </c>
     </row>
   </sheetData>
@@ -6115,7 +6161,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2756"/>
+  <dimension ref="A1:L2781"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -61286,6 +61332,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2757" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2757" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2757" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2757" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2757" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2757" s="3">
+        <v>924</v>
+      </c>
+      <c r="F2757" s="9">
+        <v>0.91100000000000003</v>
+      </c>
+    </row>
+    <row r="2758" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2758" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2758" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2758" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2758" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2758" s="3">
+        <v>80</v>
+      </c>
+      <c r="F2758" s="9">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2759" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2759" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2759" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2759" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2759" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2759" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2759" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2760" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2760" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2760" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2760" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2760" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2760" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2760" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2761" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2761" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2761" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2761" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2761" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2761" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2761" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2762" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2762" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2762" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2762" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2762" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2762" s="3">
+        <v>572</v>
+      </c>
+      <c r="F2762" s="9">
+        <v>0.89700000000000002</v>
+      </c>
+    </row>
+    <row r="2763" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2763" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2763" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2763" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2763" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2763" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2763" s="9">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="2764" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2764" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2764" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2764" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2764" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2764" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2764" s="9">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2765" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2765" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2765" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2765" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2765" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2765" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2765" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2766" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2766" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2766" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2766" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2766" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2766" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2766" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2767" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2767" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2767" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2767" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2767" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2767" s="3">
+        <v>76</v>
+      </c>
+      <c r="F2767" s="9">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="2768" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2768" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2768" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2768" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2768" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2768" s="3">
+        <v>19</v>
+      </c>
+      <c r="F2768" s="9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2769" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2769" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2769" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2769" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2769" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2769" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2769" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2770" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2770" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2770" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2770" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2770" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2770" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2770" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2771" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2771" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2771" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2771" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2771" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2771" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2771" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2772" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2772" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2772" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2772" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2772" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2772" s="3">
+        <v>163</v>
+      </c>
+      <c r="F2772" s="9">
+        <v>0.91100000000000003</v>
+      </c>
+    </row>
+    <row r="2773" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2773" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2773" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2773" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2773" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2773" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2773" s="9">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2774" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2774" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2774" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2774" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2774" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2774" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2774" s="9">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2775" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2775" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2775" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2775" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2775" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2775" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2776" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2776" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2776" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2776" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2776" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2776" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2776" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2777" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2777" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2777" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2777" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2777" s="3">
+        <v>67</v>
+      </c>
+      <c r="F2777" s="9">
+        <v>0.95699999999999996</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2778" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2778" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2778" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2778" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2778" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2778" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2779" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2779" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2779" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2779" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2779" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2779" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2780" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2780" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2780" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2780" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2780" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2780" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2781" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2781" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2781" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2781" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2781" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2781" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B668A2F-7FC6-4F6B-B244-75B4EFBDBDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F305A18-D431-44CB-9A54-679EA96D9D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="11295" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
   <sheets>
     <sheet name="리뷰수" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5816" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5868" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3482,6 +3482,29 @@
         <v>70</v>
       </c>
     </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>2026</v>
+      </c>
+      <c r="B120" t="s">
+        <v>38</v>
+      </c>
+      <c r="C120">
+        <v>899</v>
+      </c>
+      <c r="D120">
+        <v>672</v>
+      </c>
+      <c r="E120">
+        <v>127</v>
+      </c>
+      <c r="F120">
+        <v>165</v>
+      </c>
+      <c r="G120" s="17">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3490,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6151,6 +6174,29 @@
       </c>
       <c r="G119">
         <v>4.96</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>2026</v>
+      </c>
+      <c r="B120" t="s">
+        <v>38</v>
+      </c>
+      <c r="C120">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D120">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="E120">
+        <v>4.79</v>
+      </c>
+      <c r="F120">
+        <v>4.87</v>
+      </c>
+      <c r="G120">
+        <v>4.92</v>
       </c>
     </row>
   </sheetData>
@@ -6161,7 +6207,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2781"/>
+  <dimension ref="A1:L2806"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -61832,6 +61878,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2782" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2782" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2782" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2782" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2782" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2782" s="3">
+        <v>828</v>
+      </c>
+      <c r="F2782" s="9">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2783" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2783" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2783" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2783" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2783" s="3">
+        <v>54</v>
+      </c>
+      <c r="F2783" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2784" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2784" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2784" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2784" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2784" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2784" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2785" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2785" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2785" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2785" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2785" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2785" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2786" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2786" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2786" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2786" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2786" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2786" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2787" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2787" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2787" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2787" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2787" s="3">
+        <v>601</v>
+      </c>
+      <c r="F2787" s="9">
+        <v>0.89400000000000002</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2788" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2788" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2788" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2788" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2788" s="3">
+        <v>53</v>
+      </c>
+      <c r="F2788" s="9">
+        <v>7.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2789" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2789" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2789" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2789" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2789" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2789" s="9">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2790" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2790" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2790" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2790" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2790" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2790" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2791" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2791" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2791" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2791" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2791" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2791" s="9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2792" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2792" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2792" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2792" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2792" s="3">
+        <v>106</v>
+      </c>
+      <c r="F2792" s="9">
+        <v>0.83499999999999996</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2793" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2793" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2793" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2793" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2793" s="3">
+        <v>16</v>
+      </c>
+      <c r="F2793" s="9">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2794" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2794" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2794" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2794" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2794" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2794" s="9">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2795" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2795" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2795" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2795" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2795" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2795" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2796" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2796" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2796" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2796" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2796" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2797" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2797" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2797" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2797" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2797" s="3">
+        <v>146</v>
+      </c>
+      <c r="F2797" s="9">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2798" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2798" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2798" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2798" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2798" s="3">
+        <v>17</v>
+      </c>
+      <c r="F2798" s="9">
+        <v>0.10299999999999999</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2799" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2799" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2799" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2799" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2799" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2799" s="9">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2800" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2800" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2800" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2800" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2800" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2800" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2801" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2801" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2801" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2801" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2801" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2801" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2802" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2802" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2802" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2802" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2802" s="3">
+        <v>62</v>
+      </c>
+      <c r="F2802" s="9">
+        <v>0.93899999999999995</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2803" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2803" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2803" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2803" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2803" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2803" s="9">
+        <v>4.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2804" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2804" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2804" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2804" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2804" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2804" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2805" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2805" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2805" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2805" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2805" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2805" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2806" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2806" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2806" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2806" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2806" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2806" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F305A18-D431-44CB-9A54-679EA96D9D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA535229-181A-4161-BFCA-210D1D75B2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5868" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5920" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3505,6 +3505,29 @@
         <v>66</v>
       </c>
     </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>2026</v>
+      </c>
+      <c r="B121" t="s">
+        <v>39</v>
+      </c>
+      <c r="C121">
+        <v>737</v>
+      </c>
+      <c r="D121">
+        <v>587</v>
+      </c>
+      <c r="E121">
+        <v>79</v>
+      </c>
+      <c r="F121">
+        <v>167</v>
+      </c>
+      <c r="G121" s="17">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3513,7 +3536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6196,6 +6219,29 @@
         <v>4.87</v>
       </c>
       <c r="G120">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>2026</v>
+      </c>
+      <c r="B121" t="s">
+        <v>39</v>
+      </c>
+      <c r="C121">
+        <v>4.93</v>
+      </c>
+      <c r="D121">
+        <v>4.88</v>
+      </c>
+      <c r="E121">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="F121">
+        <v>4.84</v>
+      </c>
+      <c r="G121">
         <v>4.92</v>
       </c>
     </row>
@@ -6207,7 +6253,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2806"/>
+  <dimension ref="A1:L2831"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -62378,6 +62424,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2807" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2807" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2807" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2807" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2807" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2807" s="3">
+        <v>690</v>
+      </c>
+      <c r="F2807" s="9">
+        <v>0.93600000000000005</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2808" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2808" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2808" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2808" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2808" s="3">
+        <v>43</v>
+      </c>
+      <c r="F2808" s="9">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2809" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2809" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2809" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2809" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2809" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2809" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2810" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2810" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2810" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2810" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2810" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2810" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2811" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2811" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2811" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2811" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2811" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2811" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2812" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2812" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2812" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2812" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2812" s="3">
+        <v>541</v>
+      </c>
+      <c r="F2812" s="9">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2813" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2813" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2813" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2813" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2813" s="3">
+        <v>31</v>
+      </c>
+      <c r="F2813" s="9">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2814" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2814" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2814" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2814" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2814" s="3">
+        <v>8</v>
+      </c>
+      <c r="F2814" s="9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2815" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2815" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2815" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2815" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2815" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2815" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2816" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2816" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2816" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2816" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2816" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2816" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2817" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2817" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2817" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2817" s="3">
+        <v>65</v>
+      </c>
+      <c r="F2817" s="9">
+        <v>0.82299999999999995</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2818" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2818" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2818" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2818" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2818" s="3">
+        <v>13</v>
+      </c>
+      <c r="F2818" s="9">
+        <v>0.16500000000000001</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2819" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2819" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2819" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2819" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2819" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2819" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2820" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2820" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2820" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2820" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2820" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2820" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2821" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2821" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2821" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2821" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2821" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2821" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2822" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2822" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2822" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2822" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2822" s="3">
+        <v>149</v>
+      </c>
+      <c r="F2822" s="9">
+        <v>0.89200000000000002</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2823" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2823" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2823" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2823" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2823" s="3">
+        <v>11</v>
+      </c>
+      <c r="F2823" s="9">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2824" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2824" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2824" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2824" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2824" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2824" s="9">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2825" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2825" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2825" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2825" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2825" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2825" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2826" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2826" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2826" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2826" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2826" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2826" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2827" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2827" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2827" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2827" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2827" s="3">
+        <v>74</v>
+      </c>
+      <c r="F2827" s="9">
+        <v>0.94899999999999995</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2828" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2828" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2828" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2828" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2828" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2828" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2829" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2829" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2829" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2829" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2829" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2829" s="9">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2830" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2830" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2830" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2830" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2830" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2830" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2831" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2831" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2831" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2831" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2831" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2831" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA535229-181A-4161-BFCA-210D1D75B2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432E95E4-F56F-47F2-ABEE-7AE99DDC28C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5920" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5972" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3528,6 +3528,29 @@
         <v>78</v>
       </c>
     </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>2026</v>
+      </c>
+      <c r="B122" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122">
+        <v>765</v>
+      </c>
+      <c r="D122">
+        <v>536</v>
+      </c>
+      <c r="E122">
+        <v>96</v>
+      </c>
+      <c r="F122">
+        <v>157</v>
+      </c>
+      <c r="G122" s="17">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3536,7 +3559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6243,6 +6266,29 @@
       </c>
       <c r="G121">
         <v>4.92</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>2026</v>
+      </c>
+      <c r="B122" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122">
+        <v>4.88</v>
+      </c>
+      <c r="D122">
+        <v>4.91</v>
+      </c>
+      <c r="E122">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F122">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="G122">
+        <v>4.95</v>
       </c>
     </row>
   </sheetData>
@@ -6253,7 +6299,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2831"/>
+  <dimension ref="A1:L2856"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -62924,6 +62970,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2832" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2832" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2832" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2832" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2832" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2832" s="3">
+        <v>706</v>
+      </c>
+      <c r="F2832" s="9">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2833" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2833" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2833" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2833" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2833" s="3">
+        <v>38</v>
+      </c>
+      <c r="F2833" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2834" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2834" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2834" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2834" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2834" s="3">
+        <v>15</v>
+      </c>
+      <c r="F2834" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2835" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2835" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2835" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2835" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2835" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2835" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2836" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2836" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2836" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2836" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2836" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2836" s="9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2837" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2837" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2837" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2837" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2837" s="3">
+        <v>498</v>
+      </c>
+      <c r="F2837" s="9">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2838" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2838" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2838" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2838" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2838" s="3">
+        <v>30</v>
+      </c>
+      <c r="F2838" s="9">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2839" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2839" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2839" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2839" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2839" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2839" s="9">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2840" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2840" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2840" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2840" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2840" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2840" s="9">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2841" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2841" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2841" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2841" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2841" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2841" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2842" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2842" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2842" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2842" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2842" s="3">
+        <v>86</v>
+      </c>
+      <c r="F2842" s="9">
+        <v>0.89600000000000002</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2843" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2843" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2843" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2843" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2843" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2843" s="9">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2844" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2844" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2844" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2844" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2844" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2844" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2845" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2845" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2845" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2845" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2845" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2845" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2846" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2846" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2846" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2846" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2846" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2846" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2847" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2847" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2847" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2847" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2847" s="3">
+        <v>139</v>
+      </c>
+      <c r="F2847" s="9">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2848" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2848" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2848" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2848" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2848" s="3">
+        <v>12</v>
+      </c>
+      <c r="F2848" s="9">
+        <v>7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2849" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2849" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2849" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2849" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2849" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2849" s="9">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2850" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2850" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2850" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2850" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2850" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2850" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2851" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2851" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2851" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2851" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2851" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2851" s="9">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2852" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2852" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2852" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2852" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2852" s="3">
+        <v>92</v>
+      </c>
+      <c r="F2852" s="9">
+        <v>0.95799999999999996</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2853" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2853" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2853" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2853" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2853" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2853" s="9">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2854" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2854" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2854" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2854" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2854" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2854" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2855" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2855" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2855" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2855" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2855" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2855" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2856" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2856" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2856" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2856" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2856" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2856" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/통계.xlsx
+++ b/통계.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\speed\Desktop\streamlit_git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432E95E4-F56F-47F2-ABEE-7AE99DDC28C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3208AA-84A5-49EA-A566-918ADFEF618C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{F4A024DD-7AAF-4521-86D4-B48464A3C096}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5972" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6024" uniqueCount="82">
   <si>
     <t>홈던트하우스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D5E0E0-72AB-4ADE-A93E-1AF20B5B167B}">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11" style="17" bestFit="1" customWidth="1"/>
@@ -3551,6 +3551,29 @@
         <v>96</v>
       </c>
     </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>2026</v>
+      </c>
+      <c r="B123" t="s">
+        <v>41</v>
+      </c>
+      <c r="C123">
+        <v>760</v>
+      </c>
+      <c r="D123">
+        <v>573</v>
+      </c>
+      <c r="E123">
+        <v>91</v>
+      </c>
+      <c r="F123">
+        <v>148</v>
+      </c>
+      <c r="G123" s="17">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3559,7 +3582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B69A316-25FE-4EC5-81E8-130475E57CE3}">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -6289,6 +6312,29 @@
       </c>
       <c r="G122">
         <v>4.95</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>2026</v>
+      </c>
+      <c r="B123" t="s">
+        <v>41</v>
+      </c>
+      <c r="C123">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="D123">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E123">
+        <v>4.79</v>
+      </c>
+      <c r="F123">
+        <v>4.93</v>
+      </c>
+      <c r="G123">
+        <v>4.93</v>
       </c>
     </row>
   </sheetData>
@@ -6299,7 +6345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C152F69-2778-4A6D-8FC7-E721B589E33B}">
-  <dimension ref="A1:L2856"/>
+  <dimension ref="A1:L2881"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="2"/>
@@ -63470,6 +63516,506 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2857" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2857" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2857" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2857" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2857" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2857" s="3">
+        <v>699</v>
+      </c>
+      <c r="F2857" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2858" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2858" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2858" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2858" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2858" s="3">
+        <v>44</v>
+      </c>
+      <c r="F2858" s="9">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2859" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2859" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2859" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2859" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2859" s="3">
+        <v>14</v>
+      </c>
+      <c r="F2859" s="9">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2860" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2860" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2860" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2860" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2860" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2860" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2861" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2861" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2861" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2861" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2861" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2861" s="9">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2862" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2862" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2862" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2862" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2862" s="3">
+        <v>531</v>
+      </c>
+      <c r="F2862" s="9">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2863" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2863" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2863" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2863" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2863" s="3">
+        <v>30</v>
+      </c>
+      <c r="F2863" s="9">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2864" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2864" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2864" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2864" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2864" s="3">
+        <v>10</v>
+      </c>
+      <c r="F2864" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2865" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2865" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2865" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2865" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2865" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2865" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2866" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2866" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2866" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2866" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2866" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2866" s="9">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2867" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2867" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2867" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2867" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2867" s="3">
+        <v>78</v>
+      </c>
+      <c r="F2867" s="9">
+        <v>0.85699999999999998</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2868" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2868" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2868" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2868" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2868" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2868" s="9">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2869" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2869" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2869" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2869" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2869" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2869" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2870" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2870" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2870" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2870" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2870" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2871" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2871" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2871" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2871" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2871" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2871" s="9">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2872" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2872" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2872" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2872" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2872" s="3">
+        <v>138</v>
+      </c>
+      <c r="F2872" s="9">
+        <v>0.93200000000000005</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2873" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2873" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2873" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2873" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2873" s="3">
+        <v>9</v>
+      </c>
+      <c r="F2873" s="9">
+        <v>6.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2874" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2874" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2874" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2874" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2874" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2874" s="9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2875" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2875" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2875" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2875" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2875" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2875" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2876" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2876" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2876" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2876" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2876" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2876" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2877" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2877" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2877" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2877" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2877" s="3">
+        <v>79</v>
+      </c>
+      <c r="F2877" s="9">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2878" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2878" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2878" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2878" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2878" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2878" s="9">
+        <v>7.0999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2879" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2879" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2879" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2879" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2879" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2879" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2880" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2880" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2880" s="2">
+        <v>2</v>
+      </c>
+      <c r="D2880" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2880" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2880" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2881" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2881" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2881" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2881" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2881" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2881" s="9">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B1:F956" xr:uid="{1357DB43-983C-4824-A231-42A48EC12E59}"/>
   <phoneticPr fontId="1" type="noConversion"/>
